--- a/muestras/excel/Octubre Plataforma N.xlsx
+++ b/muestras/excel/Octubre Plataforma N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6dbecb95e03eb73b/Desktop/Nelson/Nueva carpeta (2)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Proyectos Activos\Consiliacion-Bancaria\muestras\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3D5C79D3-494A-4FAC-A311-52AE0DD2FEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FA87519-7AA2-4503-8D12-0F5B1742F148}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9738BCF3-A752-4966-89FC-620D8966F7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{C6B799B7-9954-44BA-90EE-B75E6CBB3802}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C6B799B7-9954-44BA-90EE-B75E6CBB3802}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>TES9040-Rut. cons. Resumen bancario</t>
   </si>
@@ -149,16 +152,28 @@
   </si>
   <si>
     <t>20-39295493-8</t>
+  </si>
+  <si>
+    <t>20-39295493-9</t>
+  </si>
+  <si>
+    <t>Provee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -529,15 +544,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34DF0620-4C87-4DC9-9DA9-B82BF8FDEF76}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +571,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -573,7 +588,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -618,7 +633,7 @@
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>45931</v>
       </c>
@@ -661,7 +676,7 @@
       </c>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>45938</v>
       </c>
@@ -705,7 +720,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>45944</v>
       </c>
@@ -728,7 +743,7 @@
         <v>2000000</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" ref="H6:H11" si="0">+H5-G6</f>
+        <f t="shared" ref="H6:H8" si="0">+H5-G6</f>
         <v>15592599.359999999</v>
       </c>
       <c r="I6" s="1">
@@ -745,7 +760,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>45944</v>
       </c>
@@ -791,7 +806,7 @@
       </c>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>45944</v>
       </c>
@@ -837,7 +852,7 @@
       </c>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>45944</v>
       </c>
@@ -854,14 +869,14 @@
         <v>45944</v>
       </c>
       <c r="F9" s="4">
-        <v>10367077.210000001</v>
+        <v>1036707.21</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="4">
         <f>+H8-G9+F9</f>
-        <v>24480693.369999997</v>
+        <v>15150323.369999997</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -883,7 +898,7 @@
       </c>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>45952</v>
       </c>
@@ -907,7 +922,7 @@
       </c>
       <c r="H10" s="4">
         <f>+H9-G10+F10</f>
-        <v>27820698.389999997</v>
+        <v>18490328.389999997</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -929,7 +944,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>45958</v>
       </c>
@@ -953,7 +968,7 @@
       </c>
       <c r="H11" s="4">
         <f>+H10-G11+F11</f>
-        <v>27661036.389999997</v>
+        <v>18330666.389999997</v>
       </c>
       <c r="I11" s="1">
         <v>73387328</v>
@@ -975,24 +990,53 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>45959</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>238</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45959</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>159662</v>
+      </c>
+      <c r="H12" s="4">
+        <f>+H11-G12+F12</f>
+        <v>18171004.389999997</v>
+      </c>
+      <c r="I12" s="1">
+        <v>73387329</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2900</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1009,7 +1053,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1026,7 +1070,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1043,7 +1087,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1060,7 +1104,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1077,7 +1121,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1095,6 +1139,7 @@
       <c r="O18" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>